--- a/zlpi.xlsx
+++ b/zlpi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCHAEFFLER PORTUGAL</t>
+          <t>SCHAEFFLER BRASIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5500001822</t>
+          <t>5441084</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -794,40 +794,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F-804661-3005-A.IR.KL</t>
+          <t>AU.3205-BD-2Z-3005-T</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3840</v>
+        <v>4608</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CW53/26</t>
+          <t>CW17/27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CW51/26</t>
+          <t>CW08/27</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3840</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCHAEFFLER PORTUGAL</t>
+          <t>SCHAEFFLER BRASIL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5500001822</t>
+          <t>5441084</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -837,40 +837,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F-804661-3005-A.IR.KL</t>
+          <t>AU.3205-BD-2Z-3005-T</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3840</v>
+        <v>2304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2027-04-12</t>
+          <t>2027-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CW15/27</t>
+          <t>CW26/27</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CW13/27</t>
+          <t>CW17/27</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2082</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCHAEFFLER PORTUGAL</t>
+          <t>SCHAEFFLER BRASIL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5500001822</t>
+          <t>5441084</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -880,40 +880,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>F-804661-3005-A.IR.KL</t>
+          <t>AU.3205-BD-2Z-3005-T</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3840</v>
+        <v>768</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2027-04-12</t>
+          <t>2027-10-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CW15/27</t>
+          <t>CW39/27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CW13/27</t>
+          <t>CW30/27</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3468</v>
+        <v>768</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCHAEFFLER PORTUGAL</t>
+          <t>SCHAEFFLER BRASIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5500001822</t>
+          <t>5441084</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -923,40 +923,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F-804661-3005-A.IR.KL</t>
+          <t>AU.3205-BD-2Z-3005-T</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7680</v>
+        <v>1536</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2027-06-28</t>
+          <t>2027-12-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CW26/27</t>
+          <t>CW48/27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CW24/27</t>
+          <t>CW39/27</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2135</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCHAEFFLER PORTUGAL</t>
+          <t>SCHAEFFLER BRASIL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5500001821</t>
+          <t>5441084</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -966,40 +966,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F-804661.03-3005-A.AU.KL</t>
+          <t>AU.3205-BD-2Z-3005-T</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3432</v>
+        <v>1536</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2028-01-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CW53/26</t>
+          <t>CW52/27</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CW51/26</t>
+          <t>CW43/27</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3432</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCHAEFFLER PORTUGAL</t>
+          <t>SCHAEFFLER BRASIL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5500001821</t>
+          <t>5441084</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1009,71 +1009,1103 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>F-804661.03-3005-A.AU.KL</t>
+          <t>AU.3205-BD-2Z-3005-T</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3432</v>
+        <v>2304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2027-04-12</t>
+          <t>2028-03-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CW15/27</t>
+          <t>CW09/28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CW13/27</t>
+          <t>CW52/27</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3432</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5441084</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AU.3205-BD-2Z-3005-T</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>690</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2028-05-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CW18/28</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CW09/28</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CW36/26</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CW27/26</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CW36/26</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CW27/26</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3120</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CW40/26</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CW31/26</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CW42/26</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CW33/26</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CW04/27</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CW48/26</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CW04/27</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CW48/26</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2027-03-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CW12/27</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CW03/27</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2027-05-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CW17/27</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CW08/27</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2027-05-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CW17/27</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CW08/27</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2027-08-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CW30/27</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CW21/27</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>960</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2027-10-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CW39/27</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CW30/27</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>960</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2027-12-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CW48/27</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CW39/27</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>960</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2027-12-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CW48/27</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CW39/27</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2028-01-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CW52/27</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CW43/27</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>480</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2028-02-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CW05/28</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CW48/27</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2028-03-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CW09/28</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CW52/27</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER BRASIL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5441085</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IR.3205-BD-2Z-3005&gt;A</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>825</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2028-05-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CW18/28</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CW09/28</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>SCHAEFFLER PORTUGAL</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5500001822</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>F-804661-3005-A.IR.KL</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3840</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CW53/26</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CW51/26</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5500001822</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>F-804661-3005-A.IR.KL</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3840</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2027-04-12</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CW15/27</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CW13/27</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5500001822</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>F-804661-3005-A.IR.KL</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3840</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2027-04-12</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CW15/27</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CW13/27</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>5500001822</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F-804661-3005-A.IR.KL</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>7680</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CW26/27</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CW24/27</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>5500001821</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>F-804661.03-3005-A.AU.KL</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E37" t="n">
+        <v>3432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CW53/26</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CW51/26</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>3432</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5500001821</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>F-804661.03-3005-A.AU.KL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3432</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2027-04-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CW15/27</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CW13/27</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>3432</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5500001821</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>F-804661.03-3005-A.AU.KL</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
         <v>8580</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>2027-06-28</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>CW26/27</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>CW24/27</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I39" t="n">
         <v>2960</v>
       </c>
     </row>
